--- a/Sufficient data WITH_PO/forecast_summary_B0BHTLF2X5_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B0BHTLF2X5_WITH_PO.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
